--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -227,7 +227,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="21">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>50</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 12/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -227,7 +227,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 12/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="21">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>50</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 12/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -227,7 +227,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 12/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="21">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>50</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -227,7 +227,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="21">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>50</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -227,7 +227,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="21">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>50</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -227,7 +227,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="21">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>50</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -227,7 +227,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1461,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="21">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>50</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="103">
   <si>
     <t>Planilla de salario y liquidación Nicaragua 2026</t>
   </si>
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -50,6 +50,12 @@
     <t>Salario neto: INSS e IR</t>
   </si>
   <si>
+    <t>Régimen integral (con enfermedad y maternidad)</t>
+  </si>
+  <si>
+    <t>Régimen de invalidez, vejez, muerte y riesgos profesionales</t>
+  </si>
+  <si>
     <t>Paso a paso</t>
   </si>
   <si>
@@ -68,9 +74,6 @@
     <t>Régimen del INSS</t>
   </si>
   <si>
-    <t>Régimen integral (con enfermedad y maternidad)</t>
-  </si>
-  <si>
     <t>Salario menos INSS</t>
   </si>
   <si>
@@ -227,7 +230,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -264,9 +267,6 @@
   </si>
   <si>
     <t>7/10/2026</t>
-  </si>
-  <si>
-    <t>Régimen de invalidez, vejez, muerte y riesgos profesionales</t>
   </si>
   <si>
     <t>Tarifa progresiva anual del IR de rentas del trabajo</t>
@@ -1030,7 +1030,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1039,29 +1039,38 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" s="8">
         <f>INDEX('Tablas oficiales'!$C$4:$C$5,MATCH(B6,'Tablas oficiales'!$B$4:$B$5,0))</f>
@@ -1069,13 +1078,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="10">
         <v>20000</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="11">
         <f>ROUND(B5*F4/100,2)</f>
@@ -1083,13 +1092,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="11">
         <f>ROUND(B5-F5,2)</f>
@@ -1097,7 +1106,7 @@
     </row>
     <row r="7" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E7" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="11">
         <f>ROUND(F6*12,2)</f>
@@ -1105,12 +1114,12 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="E8" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="11">
         <f>ROUND(IF(F7&lt;=0,0,INDEX('Tablas oficiales'!$E$8:$E$12,IFERROR(MATCH(F7,'Tablas oficiales'!$B$8:$B$12,1),1))+(F7-INDEX('Tablas oficiales'!$B$8:$B$12,IFERROR(MATCH(F7,'Tablas oficiales'!$B$8:$B$12,1),1)))*INDEX('Tablas oficiales'!$D$8:$D$12,IFERROR(MATCH(F7,'Tablas oficiales'!$B$8:$B$12,1),1))/100),2)</f>
@@ -1118,13 +1127,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="14">
         <f>F4</f>
       </c>
       <c r="E9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="11">
         <f>ROUND(F8/12,2)</f>
@@ -1132,7 +1141,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="15">
         <f>F5</f>
@@ -1140,7 +1149,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="15">
         <f>F9</f>
@@ -1148,7 +1157,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="17">
         <f>ROUND(B5-F5-F9,2)</f>
@@ -1156,14 +1165,14 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="15">
         <f>F5</f>
@@ -1171,7 +1180,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="15">
         <f>F7</f>
@@ -1179,7 +1188,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="15">
         <f>F8</f>
@@ -1187,7 +1196,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="15">
         <f>F9</f>
@@ -1195,7 +1204,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="14">
         <f>IF(COUNTIF('Tablas oficiales'!$B$8:$B$12,"&lt;"&amp;F7)=0,0,INDEX('Tablas oficiales'!$D$8:$D$12,COUNTIF('Tablas oficiales'!$B$8:$B$12,"&lt;"&amp;F7)))</f>
@@ -1203,7 +1212,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="14">
         <f>IF(B5&gt;0,ROUND(F9/B5*100,2),0)</f>
@@ -1211,7 +1220,7 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1230,8 +1239,8 @@
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B6">
-      <formula1>'Tablas oficiales'!$B$4:$B$5</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Régimen del INSS)." sqref="B6">
+      <formula1>'Salario neto'!$Z$1:$Z$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1257,25 +1266,25 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="18">
         <f>IF(B7="La parte que te toca porque dejaste el trabajo",B8,DATE(YEAR(B9),11,30))</f>
@@ -1283,16 +1292,16 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="10">
         <v>15000</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="20">
         <f>MIN(365,F4-MAX(B6,DATE(IF(MONTH(F4)=12,YEAR(F4),YEAR(F4)-1),12,1))+1)</f>
@@ -1300,7 +1309,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="21">
         <v>45352</v>
@@ -1308,35 +1317,35 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="21">
         <f>TODAY()</f>
       </c>
       <c r="C9" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1350,7 +1359,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="23">
         <f>F5</f>
@@ -1358,7 +1367,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="17">
         <f>ROUND(B5*'Tablas oficiales'!$C$14*F5/365,2)</f>
@@ -1366,7 +1375,7 @@
     </row>
     <row r="16" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1418,25 +1427,25 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="20">
         <f>IF(AND((YEAR(B6)-YEAR(B5))&gt;0,DATE(YEAR(B5)+(YEAR(B6)-YEAR(B5)),MONTH(B5),MIN(DAY(B5),DAY(EOMONTH(DATE(YEAR(B5)+(YEAR(B6)-YEAR(B5)),MONTH(B5),1),0))))&gt;B6),(YEAR(B6)-YEAR(B5))-1,(YEAR(B6)-YEAR(B5)))</f>
@@ -1444,13 +1453,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="21">
         <v>44348</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" s="20">
         <f>MIN(365,B6-DATE(YEAR(B5)+F4,MONTH(B5),MIN(DAY(B5),DAY(EOMONTH(DATE(YEAR(B5)+F4,MONTH(B5),1),0))))+1)</f>
@@ -1458,13 +1467,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="21">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6" s="24">
         <f>IF(F5=365,F4+1,F4+F5/365)</f>
@@ -1472,13 +1481,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" s="24">
         <f>IF(B7="Te despidieron por una causa del artículo 48",0,MIN('Tablas oficiales'!$C$17,IF(B7="Te despidieron sin causa justificada",MAX('Tablas oficiales'!$C$18,(MIN(F6,3)*'Tablas oficiales'!$C$15+MAX(0,F6-3)*'Tablas oficiales'!$C$16/30)),(MIN(F6,3)*'Tablas oficiales'!$C$15+MAX(0,F6-3)*'Tablas oficiales'!$C$16/30))))</f>
@@ -1486,16 +1495,16 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="10">
         <v>15000</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" s="11">
         <f>ROUND(B8*F7,2)</f>
@@ -1503,14 +1512,14 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" s="20">
         <f>MIN(365,B6-MAX(B5,DATE(IF(MONTH(B6)=12,YEAR(B6),YEAR(B6)-1),12,1))+1)</f>
@@ -1518,7 +1527,7 @@
     </row>
     <row r="10" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E10" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" s="11">
         <f>ROUND(B8*'Tablas oficiales'!$C$14*F9/365,2)</f>
@@ -1526,12 +1535,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="E11" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" s="26">
         <f>ROUND(IF(ISNUMBER(B9),B9,'Tablas oficiales'!$C$19*2*F5/365),2)</f>
@@ -1544,7 +1553,7 @@
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="E12" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" s="11">
         <f>ROUND(B8/30*F11,2)</f>
@@ -1552,7 +1561,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="27">
         <f>ROUND(F6,2)</f>
@@ -1560,7 +1569,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="28">
         <f>ROUND(F7,2)</f>
@@ -1568,7 +1577,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="15">
         <f>F8</f>
@@ -1576,7 +1585,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="23">
         <f>F9</f>
@@ -1584,7 +1593,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" s="15">
         <f>F10</f>
@@ -1592,7 +1601,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" s="28">
         <f>F11</f>
@@ -1600,7 +1609,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="15">
         <f>F12</f>
@@ -1608,7 +1617,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="17">
         <f>ROUND(F8+F10+F12,2)</f>
@@ -1616,21 +1625,21 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="27">
         <f>ROUND(F6,2)</f>
@@ -1638,7 +1647,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="28">
         <f>ROUND(F7,2)</f>
@@ -1646,7 +1655,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="17">
         <f>F8</f>
@@ -1654,7 +1663,7 @@
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1706,7 +1715,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -1717,7 +1726,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1728,71 +1737,71 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C4" s="32">
         <v>7</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="C5" s="35">
         <v>5</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1811,7 +1820,7 @@
         <v>87</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -1918,7 +1927,7 @@
         <v>96</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1941,7 +1950,7 @@
         <v>96</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1964,7 +1973,7 @@
         <v>96</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1987,7 +1996,7 @@
         <v>96</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2010,7 +2019,7 @@
         <v>96</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2033,7 +2042,7 @@
         <v>96</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -230,7 +230,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1470,7 +1470,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="21">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>51</v>

--- a/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/ni/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Liquidación»: ponés tus fechas, tu salario y cómo terminó el contrato, y te dice la indemnización por antigüedad, el aguinaldo y las vacaciones.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -230,7 +230,7 @@
     <t>Tablas oficiales de Nicaragua</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1470,7 +1470,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="21">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>51</v>
